--- a/UserScore/user_streaks.xlsx
+++ b/UserScore/user_streaks.xlsx
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>

--- a/UserScore/user_streaks.xlsx
+++ b/UserScore/user_streaks.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +497,206 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8502504224</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>O000000000O00000000O</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5164344832</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>blazetarun</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6376641431</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Anmol5678</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>46102</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8375676141</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lifeline_girl</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8495517533</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Graceful_by_mylord</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8487113041</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>𝓡𝓐𝓜𝓨𝓐</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8449546048</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>🪐 सर्वम ❄️</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6808736655</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Zaaa_00hh</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UserScore/user_streaks.xlsx
+++ b/UserScore/user_streaks.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,7 +562,7 @@
       <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="2" t="n">
         <v>46102</v>
       </c>
       <c r="F5" t="n">
@@ -632,13 +632,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -682,18 +682,68 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>46100</v>
+        <v>46102</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6248553686</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supreme2315</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8367966244</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Meraki</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46102</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/UserScore/user_streaks.xlsx
+++ b/UserScore/user_streaks.xlsx
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>46102</v>
+        <v>6</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>46103</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -737,7 +737,7 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="2" t="n">
         <v>46102</v>
       </c>
       <c r="F12" t="n">

--- a/UserScore/user_streaks.xlsx
+++ b/UserScore/user_streaks.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,16 +507,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46103</v>
+        <v>46109</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46102</v>
+        <v>46108</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46102</v>
+        <v>46108</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -632,13 +632,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46102</v>
+        <v>46106</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46102</v>
+        <v>46108</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -744,6 +744,81 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8113544293</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahaf2009</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7650673551</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Shagun</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8080437183</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Janci</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>0</v>
       </c>
     </row>
